--- a/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
+++ b/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="민원유형" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실사체크리스트" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="처리현황" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -632,7 +633,6 @@
           <t>지급명세서, 통장거래내역</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -672,7 +672,6 @@
           <t>임차계약서, 영수증</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -690,7 +689,6 @@
           <t>사진, 참석자명부</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -819,4 +817,120 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20250308-election-support-escalation</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-01T02:05:55.012+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>관리계 주무관</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S10:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>세 가지 절차·기준서를 LLM Wiki에 반영하고 DOCX·XLSX·PPTX 기성 산출물을 갱신한다. 최종 승인권자·보고 기준, 에스컬레이션 SLA, 보존기간·접근권한은 후속 확정 대상으로 관리하며 법적 근거·책임체계·RACI·개인정보 통제·대외 답변 품질관리 기준을 보완한다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>관리계의 선거비용 실사 보조 업무 범위·처리 절차·담당자 역할·기록·보고 기준, 지도계 민원문의 접수·분류·답변·유권해석 에스컬레이션 기준, 관리계·지도계 협업·인계·기록 공유 기준을 문서화한다.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>관리계 선거비용 실사 보조 절차서; 지도계 민원문의 대응 및 유권해석 에스컬레이션 기준서; 선거 사무 지원 업무분장 및 연계 기준</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/448e4540a4461526cb949c580d822376b03a001d</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
+++ b/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,6 +930,58 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20250308-election-support-escalation-approval</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-01T02:09:45.156+09:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>관리계 주무관</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S10:B10000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>세 가지 신규 절차·연계 기준서를 반영하고 산출물_설계서.docx, 요구사항_추적표.xlsx, 보고_장표.pptx 및 팀 채널 공지문 초안을 갱신 대상으로 승인한다. 최종 승인권자·법적 근거·RACI·SLA·보존기간·접근권한·대외 답변 품질관리 책임은 후속 확정 항목으로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>관리계의 선거비용 실사 보조 업무 범위, 지도계 민원문의 대응 및 유권해석 에스컬레이션 기준, 관리계·지도계 협업·인계·기록 공유 기준을 문서화하고 미확정 승인·법적 근거·RACI·SLA·보존·접근권한 항목을 후속 관리한다.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>관리계 선거비용 실사 보조 절차서; 지도계 민원문의 대응 및 유권해석 에스컬레이션 기준서; 선거 사무 지원 업무분장 및 연계 기준; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx; 팀 채널 공지문 초안</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>add;modify</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/c2afd14ec29fa1e7d491105b21c1e10438b64a21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
+++ b/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,6 +982,56 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20260731-S10-B01000-2359</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-01T02:13:33.934+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>관리계 주무관,관리계 주무관,관리계 주무관,관리계 주무관</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S10:B01000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PM 승인(HITL) · DA 통과</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>관리계 선거비용 실사 보조 절차, 지도계 민원 대응·유권해석 에스컬레이션, 관리계·지도계 협업·기록 공유 및 개인정보 통제를 반영하고 현수막 규격·기부행위 문의에 3일 처리 원칙을 적용한다. 승인권자·SLA 등 후속 확정 항목은 확인 대기 중이다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>관리계 선거비용 실사 보조 절차서; 지도계 민원문의 대응 및 유권해석 에스컬레이션 기준서; 선거 사무 지원 업무분장 및 연계 기준; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx; 팀 채널 공지문 초안</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>add;modify</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/e9a66f7be2508a784d7bd67bef55dd243eac739f</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
+++ b/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,6 +1032,56 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20250308-election-support-escalation-execution</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-01T02:17:17.513+09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>관리계 주무관</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S10:B00100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>신규 절차서·업무분장 기준서·팀 채널 공지문 초안을 추가하고 통합 산출물 3종을 갱신한 결과를 승인한다. 승인권자·법적 근거·RACI·SLA·개인정보 통제 세부사항은 후속 확정 및 시행 전 검증 대상으로 유지한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>관리계 선거비용 실사 보조 범위·처리 절차·역할·기록·보고 기준, 지도계 민원 접수·분류·답변·유권해석 에스컬레이션 기준, 현수막 규격·기부행위 해당 여부 문의, 관리계·지도계 인계·협업·기록 공유·개인정보 통제를 반영한다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>관리계 선거비용 실사 보조 절차서; 지도계 민원문의 대응 및 유권해석 에스컬레이션 기준서; 선거 사무 지원 업무분장 및 연계 기준; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx; 팀 채널 공지문 초안</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>add;modify</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/6a1b3feaf898fdbfc2f65161cb2a2a2e556a9ff8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
+++ b/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,56 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20250308-election-support-escalation-confirmation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-01T02:21:27.640+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>관리계 주무관</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S10:B00010</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>신규 절차서·업무분장 기준서·팀 채널 공지문 초안 추가와 통합 산출물 3종 수정 범위를 승인한다. 승인권자·법적 근거·RACI·SLA·개인정보 통제 및 시행 전 일관성 검증은 후속 확정·검증 대상으로 유지하며, 실제 deliverable_patch 및 GitHub Actions 실행 여부는 별도 로그로 확인한다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>관리계의 선거비용 실사 보조 범위·처리 절차·역할·권한 경계·기록·보고 기준, 지도계 민원 접수·분류·답변·유권해석 에스컬레이션 기준, 현수막 규격·기부행위 해당 여부 문의, 관리계·지도계 협업·인계·기록 공유·개인정보 통제 및 처리기한 3일 원칙을 반영한다.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>관리계 선거비용 실사 보조 절차서; 지도계 민원문의 대응 및 유권해석 에스컬레이션 기준서; 선거 사무 지원 업무분장 및 연계 기준; 팀 채널 공지문 초안; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>add;modify</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/04cf18f9eae49b880578bdbb3178f52c5efb7652</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
+++ b/scenarios/S10_election_office_support/deliverables/민원유형_실사체크리스트_시트.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,6 +1132,56 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20250308-election-support-escalation-approval-result</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-01T02:24:28.086+09:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>관리계 주무관</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bench:S10:B00001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>신규 절차서 3종과 팀 채널 공지문 초안을 추가하고 통합 산출물 3종을 수정한 실행 결과를 승인한다. 승인권자·법적 근거·공식 접수처·SLA·RACI·정보보호 통제 및 시행 전 일관성 검증은 후속 확정·검증 대상으로 유지한다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>관리계 선거비용 실사 보조 범위·처리 절차·역할·권한 경계·기록·보고 기준, 지도계 민원 접수·분류·답변·유권해석 에스컬레이션 기준, 현수막 규격·기부행위 해당 여부 문의, 관리계·지도계 인계·협업·기록 공유·개인정보 통제·처리기한 3일 원칙 및 요구사항·결정 사항·산출물 추적성을 반영한다.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>관리계 선거비용 실사 보조 절차서; 지도계 민원문의 대응 및 유권해석 에스컬레이션 기준서; 선거 사무 지원 업무분장 및 연계 기준; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx; 팀 채널 공지문 초안</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>add;modify</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/a4116126b3959fedf835145b58cddef4deac1302</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
